--- a/Employee_Reports_wi52/Kennedy Gichuhi Ngaruiya Q0510.xlsx
+++ b/Employee_Reports_wi52/Kennedy Gichuhi Ngaruiya Q0510.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-317</v>
+        <v>-325</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-37</v>
+        <v>-45</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1154,11 +1154,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1255,41 +1255,41 @@
       <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>30-Sep-2025</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>7601</v>
+        <v>7593</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
